--- a/etf_holdings/2026-10-29_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,27 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.41%2415</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2415</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.31%13,046,000</t>
+          <t>11.56%13,046,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.31%</t>
+          <t>11.56%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,40 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.3%5010</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5010</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.03%5,306,000</t>
+          <t>7.96%4,328,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.03%</t>
+          <t>7.96%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5306000</v>
+        <v>4328000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,40 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.49%4045</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.49%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4045</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.78%4,328,000</t>
+          <t>7.88%5,306,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.78%</t>
+          <t>7.88%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4328000</v>
+        <v>5306000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,27 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.45%1040</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.45%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1040</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.76%19,739,000</t>
+          <t>7.53%19,739,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.76%</t>
+          <t>7.53%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,27 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.42%3105</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3105</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.51%6,537,000</t>
+          <t>7.45%6,537,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>7.45%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,27 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.47%6405</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.47%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6405</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.73%2,512,000</t>
+          <t>5.91%2,512,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.91%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,27 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.73%543</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.73%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>543</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.60%23,519,000</t>
+          <t>4.69%23,519,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.60%</t>
+          <t>4.69%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,27 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.38%4840</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.38%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4840</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.58%2,504,000</t>
+          <t>4.45%2,504,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,27 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.52%1480</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.52%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1480</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.20%7,582,000</t>
+          <t>4.12%7,582,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,35 +1058,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.85%1250</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.85%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1250</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.15%8,937,000</t>
+          <t>4.12%8,987,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8937000</v>
+        <v>8987000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,27 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.31%1755</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.31%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1755</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.11%6,331,000</t>
+          <t>4.08%6,331,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1197,40 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.09%1390</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.09%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1390</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.64%79,618,000</t>
+          <t>3.70%7,262,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>79618000</v>
+        <v>7262000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1260,40 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-9.77%115.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-9.77%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>115.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.55%7,224,000</t>
+          <t>3.38%79,618,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7224000</v>
+        <v>79618000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,27 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.91%1115</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.91%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1115</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.24%7,636,000</t>
+          <t>3.13%7,636,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 00:00:59</t>
+          <t>2026-10-29 23:19:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,27 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.73%683</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.73%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>683</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.97%11,944,000</t>
+          <t>2.99%11,944,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,27 +1424,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.96%8170</t>
+          <t>-6.49%7640</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-6.49%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.70%923,000</t>
+          <t>2.59%923,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1482,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1517,27 +1487,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0%1950</t>
+          <t>-3.33%1885</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.29%3,281,561</t>
+          <t>2.27%3,281,561</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1545,7 +1515,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,27 +1550,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+4.32%1810</t>
+          <t>-5.8%1705</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.87%2,887,848</t>
+          <t>1.81%2,887,848</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1608,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1643,35 +1613,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+7.99%17295</t>
+          <t>-1.82%16980</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+7.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.38%223,900</t>
+          <t>1.49%238,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>223900</v>
+        <v>238900</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1706,35 +1676,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+9.33%2460</t>
+          <t>-1.42%2425</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+9.33%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.99%1,126,000</t>
+          <t>1.07%1,206,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1126000</v>
+        <v>1206000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1769,17 +1739,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3.16%277.5</t>
+          <t>-2.88%269.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+3.16%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>277.5</t>
+          <t>269.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1797,7 +1767,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1832,17 +1802,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+8.19%1585</t>
+          <t>-2.52%1545</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1860,7 +1830,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1895,27 +1865,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+9.97%3200</t>
+          <t>-10%2880</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.54%470,000</t>
+          <t>0.50%470,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1923,7 +1893,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1953,40 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.1%194.5</t>
+          <t>-0.42%236.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>236.5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.42%6,003,000</t>
+          <t>0.44%5,027,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>6003000</v>
+        <v>5027000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,40 +1986,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.23%237.5</t>
+          <t>-3.08%188.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>237.5</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.41%4,827,000</t>
+          <t>0.42%6,003,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>4827000</v>
+        <v>6003000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2084,17 +2054,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.37%214.5</t>
+          <t>-3.96%206</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2112,7 +2082,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2147,17 +2117,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+4.49%488.5</t>
+          <t>-2.35%477</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+4.49%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>488.5</t>
+          <t>477</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2175,7 +2145,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2205,40 +2175,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+3.35%4935</t>
+          <t>-7.06%84.3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>-7.06%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.14%77,000</t>
+          <t>0.12%3,921,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>77000</v>
+        <v>3921000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:11</t>
+          <t>2026-10-29 23:19:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2268,40 +2238,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.42%90.7</t>
+          <t>-5.67%4655</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>-5.67%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.13%3,921,000</t>
+          <t>0.12%69,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3921000</v>
+        <v>69000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2336,16 +2306,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+9.39%460</t>
+          <t>-4.67%438.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+9.39%</t>
+          <t>-4.67%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>460</v>
+        <v>438.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2362,7 +2332,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2397,16 +2367,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.27%159.5</t>
+          <t>-3.13%154.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-3.13%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>159.5</v>
+        <v>154.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2423,7 +2393,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2458,16 +2428,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.77%781</t>
+          <t>-3.2%756</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>781</v>
+        <v>756</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2484,7 +2454,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2519,16 +2489,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+4.67%1345</t>
+          <t>-6.32%1260</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1345</v>
+        <v>1260</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2545,7 +2515,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2580,16 +2550,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%19.75</t>
+          <t>-1.52%19.45</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.75</v>
+        <v>19.45</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2606,7 +2576,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2641,16 +2611,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+3.7%224</t>
+          <t>-4.69%213.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>224</v>
+        <v>213.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2667,7 +2637,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2702,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+2.51%285.5</t>
+          <t>-3.68%275</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+2.51%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>285.5</v>
+        <v>275</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2763,16 +2733,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+8.73%3800</t>
+          <t>-3.16%3680</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+8.73%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3800</v>
+        <v>3680</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2824,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.77%80.4</t>
+          <t>-1.37%79.3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>80.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2885,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%1140</t>
+          <t>+0.88%1150</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2946,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+5.58%6335</t>
+          <t>-8.21%5815</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+5.58%</t>
+          <t>-8.21%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6335</v>
+        <v>5815</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3007,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+5.77%550</t>
+          <t>-5.45%520</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+5.77%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3068,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.76%330</t>
+          <t>-3.64%318</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3129,12 +3099,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+8.16%477</t>
+          <t>0%477</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+8.16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:23</t>
+          <t>2026-10-29 23:19:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3190,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.5%100</t>
+          <t>+1.5%101.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>101.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:34</t>
+          <t>2026-10-29 23:19:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3251,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+4.09%2035</t>
+          <t>-4.42%1945</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+4.09%</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2035</v>
+        <v>1945</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:34</t>
+          <t>2026-10-29 23:19:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3312,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+4.3%849</t>
+          <t>-4.12%814</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>-4.12%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>849</v>
+        <v>814</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:34</t>
+          <t>2026-10-29 23:19:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3373,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+3.61%100.5</t>
+          <t>-3.28%97.2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>100.5</v>
+        <v>97.2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:34</t>
+          <t>2026-10-29 23:19:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3434,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.62%251.5</t>
+          <t>-1.39%248</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.62%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>251.5</v>
+        <v>248</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:34</t>
+          <t>2026-10-29 23:19:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3495,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+3.72%167.5</t>
+          <t>-6.57%156.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+3.72%</t>
+          <t>-6.57%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>167.5</v>
+        <v>156.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 00:01:34</t>
+          <t>2026-10-29 23:19:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3556,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+3.67%155.5</t>
+          <t>-4.5%148.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>155.5</v>
+        <v>148.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-29_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2415</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5010</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.49%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4045</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.45%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1040</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3105</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.47%6405</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.47%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6405</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.73%543</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.73%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>543</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.38%4840</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.38%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>4840</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.52%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1480</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.85%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1250</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.31%1755</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.31%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1755</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.09%1390</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.09%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1390</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.77%115.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.77%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>115.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.91%1115</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.91%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1115</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.73%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>683</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
